--- a/Fin_Proc/Emp_Mng/tests/Employee_Management_Test_Report.xlsx
+++ b/Fin_Proc/Emp_Mng/tests/Employee_Management_Test_Report.xlsx
@@ -40,7 +40,7 @@
     <t>Project Assigned Date:</t>
   </si>
   <si>
-    <t>2026-07-08</t>
+    <t>2026-07-09</t>
   </si>
   <si>
     <t>Module Name:</t>
